--- a/data/manual/eu_wob_prices.xlsx
+++ b/data/manual/eu_wob_prices.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E946DD16-E916-45F7-8274-E0BC3F75C96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95B3CBD2-3D24-4B70-96E3-C18138CEE153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28335" yWindow="420" windowWidth="21600" windowHeight="12585" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
+    <workbookView xWindow="1536" yWindow="720" windowWidth="12780" windowHeight="13680" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -65,87 +65,6 @@
     <t>t</t>
   </si>
   <si>
-    <t>Austria</t>
-  </si>
-  <si>
-    <t>Belgium</t>
-  </si>
-  <si>
-    <t>Bulgaria</t>
-  </si>
-  <si>
-    <t>Croatia</t>
-  </si>
-  <si>
-    <t>Cyprus</t>
-  </si>
-  <si>
-    <t>Czechia</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Estonia</t>
-  </si>
-  <si>
-    <t>Finland</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>Greece</t>
-  </si>
-  <si>
-    <t>Hungary</t>
-  </si>
-  <si>
-    <t>Ireland</t>
-  </si>
-  <si>
-    <t>Italy</t>
-  </si>
-  <si>
-    <t>Latvia</t>
-  </si>
-  <si>
-    <t>Lithuania</t>
-  </si>
-  <si>
-    <t>Luxembourg</t>
-  </si>
-  <si>
-    <t>Malta</t>
-  </si>
-  <si>
-    <t>Netherlands</t>
-  </si>
-  <si>
-    <t>Poland</t>
-  </si>
-  <si>
-    <t>Portugal</t>
-  </si>
-  <si>
-    <t>Romania</t>
-  </si>
-  <si>
-    <t>Slovakia</t>
-  </si>
-  <si>
-    <t>Slovenia</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>Sweden</t>
-  </si>
-  <si>
     <t>CE/EC/EG EUR27_2020 (IV)
 Moyenne pondérée
 Weighted average
@@ -156,6 +75,87 @@
 Moyenne pondérée
 Weighted average
 Gewichteter Durchschnitt</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Bulgaria</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Cyprus</t>
+  </si>
+  <si>
+    <t>Czechia</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Estonia</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Greece</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Latvia</t>
+  </si>
+  <si>
+    <t>Lithuania</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Malta</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Slovakia</t>
+  </si>
+  <si>
+    <t>Slovenia</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Sweden</t>
   </si>
 </sst>
 </file>
@@ -163,10 +163,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,7 +237,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -245,12 +245,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -272,9 +272,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -312,7 +312,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -418,7 +418,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -560,7 +560,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -569,13 +569,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0029BEF-67EA-4961-8BA2-85692E8FD29E}">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="7" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="7" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="135">
+    <row r="1" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,9 +598,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -621,94 +621,94 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="C3" s="3">
-        <v>1931</v>
+        <v>2050</v>
       </c>
       <c r="D3" s="3">
-        <v>1538.12</v>
+        <v>1615.85</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1856.1</v>
+        <v>1882.74</v>
       </c>
       <c r="C4" s="3">
-        <v>2059.94</v>
+        <v>2179.35</v>
       </c>
       <c r="D4" s="3">
-        <v>1249.8</v>
+        <v>1367.2</v>
       </c>
       <c r="E4" s="3">
-        <v>517.28</v>
+        <v>518.15</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1476.9</v>
+        <v>1533.3</v>
       </c>
       <c r="C5" s="3">
-        <v>1578</v>
+        <v>1742.6</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>615.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1601</v>
+        <v>1691</v>
       </c>
       <c r="C6" s="3">
-        <v>1721</v>
+        <v>1889</v>
       </c>
       <c r="D6" s="3">
-        <v>1115</v>
+        <v>1425</v>
       </c>
       <c r="E6" s="3">
-        <v>794.6</v>
+        <v>869.63</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1484.92</v>
+        <v>1561.22</v>
       </c>
       <c r="C7" s="3">
-        <v>1595.42</v>
+        <v>1698</v>
       </c>
       <c r="D7" s="3">
-        <v>1372.69</v>
+        <v>1380.14</v>
       </c>
       <c r="E7" s="3">
         <v>1059.51</v>
@@ -716,127 +716,127 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1720.2563042579577</v>
+        <v>1744.3609022556391</v>
       </c>
       <c r="C8" s="3">
-        <v>1707.1930549813972</v>
+        <v>1843.7990580847722</v>
       </c>
       <c r="D8" s="3">
-        <v>1267.920628358826</v>
+        <v>1378.9969429067173</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>912.0297643654402</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>916.30174336941252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>2458.6655251752368</v>
+        <v>2458.8957711808853</v>
       </c>
       <c r="C9" s="3">
-        <v>2183.102359676815</v>
+        <v>2263.5754324472568</v>
       </c>
       <c r="D9" s="3">
-        <v>2268.9817539729252</v>
+        <v>2349.4628690684826</v>
       </c>
       <c r="E9" s="3">
-        <v>1541.173952592434</v>
+        <v>1541.3182785053982</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>1742</v>
+        <v>1812</v>
       </c>
       <c r="C10" s="3">
-        <v>1757</v>
+        <v>1877</v>
       </c>
       <c r="D10" s="3">
-        <v>1356</v>
+        <v>1417</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>2162.9499999999994</v>
+        <v>2196.3636363636365</v>
       </c>
       <c r="C11" s="3">
-        <v>2195.8999999999996</v>
+        <v>2337.4090909090914</v>
       </c>
       <c r="D11" s="3">
-        <v>1816.1377777777777</v>
+        <v>1921.473611111111</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>2010.09</v>
+        <v>2065.9</v>
       </c>
       <c r="C12" s="3">
-        <v>2066.41</v>
+        <v>2215.8200000000002</v>
       </c>
       <c r="D12" s="3">
-        <v>1605.26</v>
+        <v>1711.89</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>1007.85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>1016.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>2192</v>
+        <v>2184</v>
       </c>
       <c r="C13" s="3">
-        <v>2158</v>
+        <v>2208</v>
       </c>
       <c r="D13" s="3">
-        <v>1339.1</v>
+        <v>1285.2</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>1094.25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>1077.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>1977</v>
+        <v>2020</v>
       </c>
       <c r="C14" s="3">
-        <v>1950</v>
+        <v>2064</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3">
@@ -845,125 +845,125 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>1641.76701259167</v>
+        <v>1647.3912982776906</v>
       </c>
       <c r="C15" s="3">
-        <v>1686.8726442507264</v>
+        <v>1824.4035524807432</v>
       </c>
       <c r="D15" s="3">
-        <v>1686.8726442507264</v>
+        <v>1824.4035524807432</v>
       </c>
       <c r="E15" s="3">
-        <v>1076.5186107651859</v>
+        <v>1091.0489587339964</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>973.56748304967471</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>964.29188511218581</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16" s="3">
-        <v>1720.2</v>
+        <v>1817.3</v>
       </c>
       <c r="C16" s="3">
-        <v>1695</v>
+        <v>1845.6</v>
       </c>
       <c r="D16" s="3">
-        <v>1262.95</v>
+        <v>1360.95</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>1910.32</v>
+        <v>1992.3</v>
       </c>
       <c r="C17" s="3">
-        <v>2038.17</v>
+        <v>2090.25</v>
       </c>
       <c r="D17" s="3">
-        <v>1794.6</v>
+        <v>1878.2</v>
       </c>
       <c r="E17" s="3">
-        <v>647.82000000000005</v>
+        <v>676.09</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>760.32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>756.81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1812.25</v>
+        <v>1874</v>
       </c>
       <c r="C18" s="3">
-        <v>1797.8</v>
+        <v>1940</v>
       </c>
       <c r="D18" s="3">
-        <v>1482</v>
+        <v>1624.2</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>908.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1769.23</v>
+        <v>1800.48</v>
       </c>
       <c r="C19" s="3">
-        <v>1926.78</v>
+        <v>2034.95</v>
       </c>
       <c r="D19" s="3">
-        <v>1338.26</v>
+        <v>1395.71</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>742.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>752.97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1726</v>
+        <v>1708</v>
       </c>
       <c r="C20" s="3">
-        <v>1804</v>
+        <v>1853</v>
       </c>
       <c r="D20" s="3">
-        <v>1299</v>
+        <v>1344</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B21" s="3">
         <v>1340</v>
@@ -978,206 +978,206 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>2340.59</v>
+        <v>2369.7199999999998</v>
       </c>
       <c r="C22" s="3">
-        <v>2309.81</v>
+        <v>2413.94</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>935.57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>923.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1681.9030286726393</v>
+        <v>1755.8680367768811</v>
       </c>
       <c r="C23" s="3">
-        <v>1724.8046918186569</v>
+        <v>1878.8271459641207</v>
       </c>
       <c r="D23" s="3">
-        <v>1397.5617669040516</v>
+        <v>1504.5120536311176</v>
       </c>
       <c r="E23" s="3">
-        <v>686.38663220611227</v>
+        <v>738.79280082133005</v>
       </c>
       <c r="F23" s="3">
-        <v>551.95219542223128</v>
+        <v>561.67898374078197</v>
       </c>
       <c r="G23" s="3">
-        <v>721.37765914698434</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>708.00670067649025</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>1972</v>
+        <v>1982</v>
       </c>
       <c r="C24" s="3">
-        <v>1960</v>
+        <v>2049</v>
       </c>
       <c r="D24" s="3">
-        <v>1948</v>
+        <v>2056</v>
       </c>
       <c r="E24" s="3">
-        <v>997.62</v>
+        <v>1075.56</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>1720.716302854526</v>
+        <v>1802.6708607377752</v>
       </c>
       <c r="C25" s="3">
-        <v>1888.440696076935</v>
+        <v>2027.6141454580118</v>
       </c>
       <c r="D25" s="3">
-        <v>1196.6512746145627</v>
+        <v>1398.9686397864837</v>
       </c>
       <c r="E25" s="3">
-        <v>766.9229888566631</v>
+        <v>894.63730816890666</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>870.8632269882462</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>875.40749213611673</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>1713</v>
+        <v>1761</v>
       </c>
       <c r="C26" s="3">
-        <v>1668</v>
+        <v>1809</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1586.6</v>
+        <v>1649.42</v>
       </c>
       <c r="C27" s="3">
-        <v>1689.62</v>
+        <v>1864.74</v>
       </c>
       <c r="D27" s="3">
-        <v>1330.57</v>
+        <v>1496.04</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>964.41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>957.46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1581.92</v>
+        <v>1687.0427519999998</v>
       </c>
       <c r="C28" s="3">
-        <v>1622.43</v>
+        <v>1793.914818</v>
       </c>
       <c r="D28" s="3">
-        <v>1196.26</v>
+        <v>1269.99</v>
       </c>
       <c r="E28" s="3">
-        <v>621.12</v>
+        <v>671.8</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>1047.94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>1056.724602</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1439.112720688094</v>
+        <v>1452.501251763849</v>
       </c>
       <c r="C29" s="3">
-        <v>1706.8356722498868</v>
+        <v>1824.8440985024351</v>
       </c>
       <c r="D29" s="3">
-        <v>1584.2462652784063</v>
+        <v>1699.7587509672719</v>
       </c>
       <c r="E29" s="3">
-        <v>959.43866002716152</v>
+        <v>1001.6841913605534</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
     </row>
-    <row r="30" spans="1:7" ht="76.5">
+    <row r="30" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>1908.6170281037569</v>
+        <v>1952.2438849994655</v>
       </c>
       <c r="C30" s="5">
-        <v>1927.776862870476</v>
+        <v>2043.111462258574</v>
       </c>
       <c r="D30" s="5">
-        <v>1411.7219216036237</v>
+        <v>1443.1082954834305</v>
       </c>
       <c r="E30" s="5">
-        <v>659.59927540044248</v>
+        <v>705.33154874150307</v>
       </c>
       <c r="F30" s="5">
-        <v>531.19293143511197</v>
+        <v>540.55388921955785</v>
       </c>
       <c r="G30" s="5">
-        <v>850.83758779532934</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="76.5">
+        <v>847.81487888773756</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>1962.42792576275</v>
+        <v>2005.586157662613</v>
       </c>
       <c r="C31" s="5">
-        <v>1968.1175641276711</v>
+        <v>2077.5444878280177</v>
       </c>
       <c r="D31" s="5">
-        <v>1395.6673760791923</v>
+        <v>1422.0891706281802</v>
       </c>
       <c r="E31" s="5">
-        <v>678.72586703396792</v>
+        <v>725.70989019798674</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>881.26449455603597</v>
+        <v>880.56178866999812</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual/eu_wob_prices.xlsx
+++ b/data/manual/eu_wob_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95B3CBD2-3D24-4B70-96E3-C18138CEE153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D0EE689-4616-427A-91B3-56B51B4EFCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="720" windowWidth="12780" windowHeight="13680" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
+    <workbookView xWindow="2688" yWindow="720" windowWidth="12348" windowHeight="13680" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -600,7 +600,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -626,13 +626,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>1838</v>
+        <v>1721</v>
       </c>
       <c r="C3" s="3">
-        <v>2050</v>
+        <v>1965</v>
       </c>
       <c r="D3" s="3">
-        <v>1615.85</v>
+        <v>1542.87</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -643,20 +643,20 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1882.74</v>
+        <v>1813.94</v>
       </c>
       <c r="C4" s="3">
-        <v>2179.35</v>
+        <v>2156.79</v>
       </c>
       <c r="D4" s="3">
-        <v>1367.2</v>
+        <v>1229.0999999999999</v>
       </c>
       <c r="E4" s="3">
-        <v>518.15</v>
+        <v>503.75</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>842</v>
+        <v>817</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -664,7 +664,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1533.3</v>
+        <v>1533</v>
       </c>
       <c r="C5" s="3">
         <v>1742.6</v>
@@ -681,20 +681,20 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1691</v>
+        <v>1685</v>
       </c>
       <c r="C6" s="3">
-        <v>1889</v>
+        <v>1903</v>
       </c>
       <c r="D6" s="3">
-        <v>1425</v>
+        <v>1445</v>
       </c>
       <c r="E6" s="3">
         <v>869.63</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>777</v>
+        <v>744</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -702,13 +702,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1561.22</v>
+        <v>1593.48</v>
       </c>
       <c r="C7" s="3">
-        <v>1698</v>
+        <v>1783.28</v>
       </c>
       <c r="D7" s="3">
-        <v>1380.14</v>
+        <v>1437.39</v>
       </c>
       <c r="E7" s="3">
         <v>1059.51</v>
@@ -721,18 +721,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1744.3609022556391</v>
+        <v>1703.1172686788718</v>
       </c>
       <c r="C8" s="3">
-        <v>1843.7990580847722</v>
+        <v>1813.1700478311066</v>
       </c>
       <c r="D8" s="3">
-        <v>1378.9969429067173</v>
+        <v>1275.152564736929</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>916.30174336941252</v>
+        <v>914.23387761834078</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -740,16 +740,16 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>2458.8957711808853</v>
+        <v>2324.8348002889325</v>
       </c>
       <c r="C9" s="3">
-        <v>2263.5754324472568</v>
+        <v>2142.9144706920997</v>
       </c>
       <c r="D9" s="3">
-        <v>2349.4628690684826</v>
+        <v>2228.7915674576634</v>
       </c>
       <c r="E9" s="3">
-        <v>1541.3182785053982</v>
+        <v>1541.1327215816368</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -759,13 +759,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>1812</v>
+        <v>1717</v>
       </c>
       <c r="C10" s="3">
-        <v>1877</v>
+        <v>1825</v>
       </c>
       <c r="D10" s="3">
-        <v>1417</v>
+        <v>1362</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -778,13 +778,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>2196.3636363636365</v>
+        <v>2165.083333333333</v>
       </c>
       <c r="C11" s="3">
-        <v>2337.4090909090914</v>
+        <v>2334.208333333333</v>
       </c>
       <c r="D11" s="3">
-        <v>1921.473611111111</v>
+        <v>1789.4102777777775</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -795,18 +795,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>2065.9</v>
+        <v>2014.06</v>
       </c>
       <c r="C12" s="3">
-        <v>2215.8200000000002</v>
+        <v>2169.04</v>
       </c>
       <c r="D12" s="3">
-        <v>1711.89</v>
+        <v>1646.17</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>1016.6</v>
+        <v>1018.11</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -814,18 +814,18 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>2184</v>
+        <v>2143</v>
       </c>
       <c r="C13" s="3">
-        <v>2208</v>
+        <v>2149</v>
       </c>
       <c r="D13" s="3">
-        <v>1285.2</v>
+        <v>1315.7</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>1077.75</v>
+        <v>1090.3800000000001</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -833,10 +833,10 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>2020</v>
+        <v>1980</v>
       </c>
       <c r="C14" s="3">
-        <v>2064</v>
+        <v>1986</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3">
@@ -850,20 +850,20 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>1647.3912982776906</v>
+        <v>1581.6491883413139</v>
       </c>
       <c r="C15" s="3">
-        <v>1824.4035524807432</v>
+        <v>1812.0669337748488</v>
       </c>
       <c r="D15" s="3">
-        <v>1824.4035524807432</v>
+        <v>1812.0669337748488</v>
       </c>
       <c r="E15" s="3">
-        <v>1091.0489587339964</v>
+        <v>1092.03904853568</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>964.29188511218581</v>
+        <v>964.71104030983986</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -871,13 +871,13 @@
         <v>24</v>
       </c>
       <c r="B16" s="3">
-        <v>1817.3</v>
+        <v>1837.1</v>
       </c>
       <c r="C16" s="3">
-        <v>1845.6</v>
+        <v>1900.6</v>
       </c>
       <c r="D16" s="3">
-        <v>1360.95</v>
+        <v>1355.35</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -888,20 +888,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>1992.3</v>
+        <v>1992.63</v>
       </c>
       <c r="C17" s="3">
-        <v>2090.25</v>
+        <v>2080.8000000000002</v>
       </c>
       <c r="D17" s="3">
-        <v>1878.2</v>
+        <v>1809</v>
       </c>
       <c r="E17" s="3">
-        <v>676.09</v>
+        <v>645.17999999999995</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>756.81</v>
+        <v>760.1</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -909,18 +909,18 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1874</v>
+        <v>1802</v>
       </c>
       <c r="C18" s="3">
-        <v>1940</v>
+        <v>1898</v>
       </c>
       <c r="D18" s="3">
-        <v>1624.2</v>
+        <v>1582.2</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>908.5</v>
+        <v>913.25</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -928,18 +928,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1800.48</v>
+        <v>1755.95</v>
       </c>
       <c r="C19" s="3">
-        <v>2034.95</v>
+        <v>1995.96</v>
       </c>
       <c r="D19" s="3">
-        <v>1395.71</v>
+        <v>1314.71</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>752.97</v>
+        <v>749.3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -947,10 +947,10 @@
         <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1708</v>
+        <v>1619</v>
       </c>
       <c r="C20" s="3">
-        <v>1853</v>
+        <v>1798</v>
       </c>
       <c r="D20" s="3">
         <v>1344</v>
@@ -983,16 +983,16 @@
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>2369.7199999999998</v>
+        <v>2290.1</v>
       </c>
       <c r="C22" s="3">
-        <v>2413.94</v>
+        <v>2322.65</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>923.8</v>
+        <v>930.27</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1000,22 +1000,22 @@
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1755.8680367768811</v>
+        <v>1696.1974419840192</v>
       </c>
       <c r="C23" s="3">
-        <v>1878.8271459641207</v>
+        <v>1863.7903215316137</v>
       </c>
       <c r="D23" s="3">
-        <v>1504.5120536311176</v>
+        <v>1390.7366776744891</v>
       </c>
       <c r="E23" s="3">
-        <v>738.79280082133005</v>
+        <v>697.67057171113061</v>
       </c>
       <c r="F23" s="3">
-        <v>561.67898374078197</v>
+        <v>527.21760906814291</v>
       </c>
       <c r="G23" s="3">
-        <v>708.00670067649025</v>
+        <v>700.9919130107985</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1023,20 +1023,20 @@
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>1982</v>
+        <v>1896</v>
       </c>
       <c r="C24" s="3">
-        <v>2049</v>
+        <v>1975</v>
       </c>
       <c r="D24" s="3">
-        <v>2056</v>
+        <v>1974</v>
       </c>
       <c r="E24" s="3">
-        <v>1075.56</v>
+        <v>1060.9327320323966</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>891</v>
+        <v>886</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1044,20 +1044,20 @@
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>1802.6708607377752</v>
+        <v>1791.1487040604202</v>
       </c>
       <c r="C25" s="3">
-        <v>2027.6141454580118</v>
+        <v>2012.8125417199094</v>
       </c>
       <c r="D25" s="3">
-        <v>1398.9686397864837</v>
+        <v>1347.6570098983466</v>
       </c>
       <c r="E25" s="3">
-        <v>894.63730816890666</v>
+        <v>899.30578071062121</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>875.40749213611673</v>
+        <v>880.57139587664267</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1065,16 +1065,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>1761</v>
+        <v>1701</v>
       </c>
       <c r="C26" s="3">
-        <v>1809</v>
+        <v>1833</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1082,18 +1082,18 @@
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1649.42</v>
+        <v>1618.62</v>
       </c>
       <c r="C27" s="3">
-        <v>1864.74</v>
+        <v>1877.58</v>
       </c>
       <c r="D27" s="3">
-        <v>1496.04</v>
+        <v>1518.46</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>957.46</v>
+        <v>959.94</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1101,20 +1101,20 @@
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1687.0427519999998</v>
+        <v>1702.8721639999999</v>
       </c>
       <c r="C28" s="3">
-        <v>1793.914818</v>
+        <v>1821.570894</v>
       </c>
       <c r="D28" s="3">
-        <v>1269.99</v>
+        <v>1291.433</v>
       </c>
       <c r="E28" s="3">
-        <v>671.8</v>
+        <v>681.02</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>1056.724602</v>
+        <v>1063.401222</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1122,16 +1122,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1452.501251763849</v>
+        <v>1307.6467101363367</v>
       </c>
       <c r="C29" s="3">
-        <v>1824.8440985024351</v>
+        <v>1680.1787424194063</v>
       </c>
       <c r="D29" s="3">
-        <v>1699.7587509672719</v>
+        <v>1595.9144589849984</v>
       </c>
       <c r="E29" s="3">
-        <v>1001.6841913605534</v>
+        <v>962.74679677169297</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1141,22 +1141,22 @@
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>1952.2438849994655</v>
+        <v>1910.6851872645709</v>
       </c>
       <c r="C30" s="5">
-        <v>2043.111462258574</v>
+        <v>2012.6737914623579</v>
       </c>
       <c r="D30" s="5">
-        <v>1443.1082954834305</v>
+        <v>1416.5923332126035</v>
       </c>
       <c r="E30" s="5">
-        <v>705.33154874150307</v>
+        <v>707.8682838293422</v>
       </c>
       <c r="F30" s="5">
-        <v>540.55388921955785</v>
+        <v>507.38862819611103</v>
       </c>
       <c r="G30" s="5">
-        <v>847.81487888773756</v>
+        <v>849.52154138876108</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
@@ -1164,20 +1164,20 @@
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>2005.586157662613</v>
+        <v>1973.2203897654731</v>
       </c>
       <c r="C31" s="5">
-        <v>2077.5444878280177</v>
+        <v>2049.2286117722501</v>
       </c>
       <c r="D31" s="5">
-        <v>1422.0891706281802</v>
+        <v>1399.6065576790299</v>
       </c>
       <c r="E31" s="5">
-        <v>725.70989019798674</v>
+        <v>729.02609697800733</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>880.56178866999812</v>
+        <v>884.38549946409216</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual/eu_wob_prices.xlsx
+++ b/data/manual/eu_wob_prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D0EE689-4616-427A-91B3-56B51B4EFCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBC795CF-7EF1-4F68-953A-923CE5A09F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="720" windowWidth="12348" windowHeight="13680" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -569,13 +569,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0029BEF-67EA-4961-8BA2-85692E8FD29E}">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="2" max="7" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="7" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,9 +598,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -621,94 +621,94 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>1721</v>
+        <v>1795</v>
       </c>
       <c r="C3" s="3">
-        <v>1965</v>
+        <v>2043</v>
       </c>
       <c r="D3" s="3">
-        <v>1542.87</v>
+        <v>1600.91</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1813.94</v>
+        <v>1841.05</v>
       </c>
       <c r="C4" s="3">
-        <v>2156.79</v>
+        <v>2173.52</v>
       </c>
       <c r="D4" s="3">
-        <v>1229.0999999999999</v>
+        <v>1318.7</v>
       </c>
       <c r="E4" s="3">
-        <v>503.75</v>
+        <v>525.77</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1533</v>
+        <v>1534.9</v>
       </c>
       <c r="C5" s="3">
-        <v>1742.6</v>
+        <v>1767.5</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>642.79999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1685</v>
+        <v>1623</v>
       </c>
       <c r="C6" s="3">
-        <v>1903</v>
+        <v>1835</v>
       </c>
       <c r="D6" s="3">
-        <v>1445</v>
+        <v>1360</v>
       </c>
       <c r="E6" s="3">
-        <v>869.63</v>
+        <v>869.6</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1593.48</v>
+        <v>1594.98</v>
       </c>
       <c r="C7" s="3">
-        <v>1783.28</v>
+        <v>1804.46</v>
       </c>
       <c r="D7" s="3">
-        <v>1437.39</v>
+        <v>1449.28</v>
       </c>
       <c r="E7" s="3">
         <v>1059.51</v>
@@ -716,56 +716,54 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1703.1172686788718</v>
+        <v>1713.5242345357628</v>
       </c>
       <c r="C8" s="3">
-        <v>1813.1700478311066</v>
+        <v>1843.9733895293582</v>
       </c>
       <c r="D8" s="3">
-        <v>1275.152564736929</v>
+        <v>1347.9608280649559</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>914.23387761834078</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>915.58200074377089</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>2324.8348002889325</v>
+        <v>2445.2232536986007</v>
       </c>
       <c r="C9" s="3">
-        <v>2142.9144706920997</v>
+        <v>2249.9264292784719</v>
       </c>
       <c r="D9" s="3">
-        <v>2228.7915674576634</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1541.1327215816368</v>
-      </c>
+        <v>2335.8035260440352</v>
+      </c>
+      <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>1717</v>
+        <v>1772</v>
       </c>
       <c r="C10" s="3">
-        <v>1825</v>
+        <v>1880</v>
       </c>
       <c r="D10" s="3">
-        <v>1362</v>
+        <v>1421</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -773,70 +771,70 @@
         <v>969</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>2165.083333333333</v>
+        <v>2140.3478260869565</v>
       </c>
       <c r="C11" s="3">
-        <v>2334.208333333333</v>
+        <v>2317.652173913043</v>
       </c>
       <c r="D11" s="3">
-        <v>1789.4102777777775</v>
+        <v>1865.4152777777779</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>2014.06</v>
+        <v>2038.33</v>
       </c>
       <c r="C12" s="3">
-        <v>2169.04</v>
+        <v>2199.34</v>
       </c>
       <c r="D12" s="3">
-        <v>1646.17</v>
+        <v>1696.18</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>1018.11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1019.64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>2143</v>
+        <v>2239</v>
       </c>
       <c r="C13" s="3">
-        <v>2149</v>
+        <v>2266</v>
       </c>
       <c r="D13" s="3">
-        <v>1315.7</v>
+        <v>1343</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>1090.3800000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>1980</v>
+        <v>2002</v>
       </c>
       <c r="C14" s="3">
-        <v>1986</v>
+        <v>1996</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3">
@@ -845,123 +843,123 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>1581.6491883413139</v>
+        <v>1615.0576393983818</v>
       </c>
       <c r="C15" s="3">
-        <v>1812.0669337748488</v>
+        <v>1859.8302373451172</v>
       </c>
       <c r="D15" s="3">
-        <v>1812.0669337748488</v>
+        <v>1859.8302373451172</v>
       </c>
       <c r="E15" s="3">
-        <v>1092.03904853568</v>
+        <v>1097.2287458900892</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>964.71104030983986</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>987.25766439386553</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="3">
-        <v>1837.1</v>
+        <v>1838.7</v>
       </c>
       <c r="C16" s="3">
-        <v>1900.6</v>
+        <v>1900.8</v>
       </c>
       <c r="D16" s="3">
-        <v>1355.35</v>
+        <v>1348.75</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>1992.63</v>
+        <v>1987.99</v>
       </c>
       <c r="C17" s="3">
-        <v>2080.8000000000002</v>
+        <v>2078.92</v>
       </c>
       <c r="D17" s="3">
-        <v>1809</v>
+        <v>1857.45</v>
       </c>
       <c r="E17" s="3">
-        <v>645.17999999999995</v>
+        <v>646.17999999999995</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>760.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>771.37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1802</v>
+        <v>1816.8</v>
       </c>
       <c r="C18" s="3">
-        <v>1898</v>
+        <v>1913.5</v>
       </c>
       <c r="D18" s="3">
-        <v>1582.2</v>
+        <v>1597.68</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>913.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1755.95</v>
+        <v>1770.05</v>
       </c>
       <c r="C19" s="3">
-        <v>1995.96</v>
+        <v>2031.03</v>
       </c>
       <c r="D19" s="3">
-        <v>1314.71</v>
+        <v>1381.47</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>749.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>752.45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1619</v>
+        <v>1727</v>
       </c>
       <c r="C20" s="3">
-        <v>1798</v>
+        <v>1922</v>
       </c>
       <c r="D20" s="3">
-        <v>1344</v>
+        <v>1415</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -978,97 +976,97 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>2290.1</v>
+        <v>2328.81</v>
       </c>
       <c r="C22" s="3">
-        <v>2322.65</v>
+        <v>2383.12</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>930.27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>938.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1696.1974419840192</v>
+        <v>1480.8336577669313</v>
       </c>
       <c r="C23" s="3">
-        <v>1863.7903215316137</v>
+        <v>1685.5407719552709</v>
       </c>
       <c r="D23" s="3">
-        <v>1390.7366776744891</v>
+        <v>1463.6894449163976</v>
       </c>
       <c r="E23" s="3">
-        <v>697.67057171113061</v>
+        <v>717.28883590534349</v>
       </c>
       <c r="F23" s="3">
-        <v>527.21760906814291</v>
+        <v>555.43504138104333</v>
       </c>
       <c r="G23" s="3">
-        <v>700.9919130107985</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>692.2868079227153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>1896</v>
+        <v>1954</v>
       </c>
       <c r="C24" s="3">
-        <v>1975</v>
+        <v>2026</v>
       </c>
       <c r="D24" s="3">
-        <v>1974</v>
+        <v>2024</v>
       </c>
       <c r="E24" s="3">
-        <v>1060.9327320323966</v>
+        <v>1032.83</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>1791.1487040604202</v>
+        <v>1816.3889684130165</v>
       </c>
       <c r="C25" s="3">
-        <v>2012.8125417199094</v>
+        <v>2029.6688615325893</v>
       </c>
       <c r="D25" s="3">
-        <v>1347.6570098983466</v>
+        <v>1394.7094188376755</v>
       </c>
       <c r="E25" s="3">
-        <v>899.30578071062121</v>
+        <v>843.17014982345654</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>880.57139587664267</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>885.02147151445752</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>1701</v>
+        <v>1696</v>
       </c>
       <c r="C26" s="3">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1077,107 +1075,107 @@
         <v>774</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1618.62</v>
+        <v>1577.66</v>
       </c>
       <c r="C27" s="3">
-        <v>1877.58</v>
+        <v>1844.53</v>
       </c>
       <c r="D27" s="3">
-        <v>1518.46</v>
+        <v>1433.31</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>959.94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>971.54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1702.8721639999999</v>
+        <v>1705.449251</v>
       </c>
       <c r="C28" s="3">
-        <v>1821.570894</v>
+        <v>1828.8145149999998</v>
       </c>
       <c r="D28" s="3">
-        <v>1291.433</v>
+        <v>1323.2560000000001</v>
       </c>
       <c r="E28" s="3">
-        <v>681.02</v>
+        <v>648.80999999999995</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>1063.401222</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1075.7977460000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1307.6467101363367</v>
+        <v>1408.2356149440959</v>
       </c>
       <c r="C29" s="3">
-        <v>1680.1787424194063</v>
+        <v>1779.8381965275885</v>
       </c>
       <c r="D29" s="3">
-        <v>1595.9144589849984</v>
+        <v>1670.3026997545678</v>
       </c>
       <c r="E29" s="3">
-        <v>962.74679677169297</v>
+        <v>984.9104626852104</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
     </row>
-    <row r="30" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>1910.6851872645709</v>
+        <v>1923.6200449931841</v>
       </c>
       <c r="C30" s="5">
-        <v>2012.6737914623579</v>
+        <v>2033.1381469525866</v>
       </c>
       <c r="D30" s="5">
-        <v>1416.5923332126035</v>
+        <v>1458.7022912064526</v>
       </c>
       <c r="E30" s="5">
-        <v>707.8682838293422</v>
+        <v>681.83587524575557</v>
       </c>
       <c r="F30" s="5">
-        <v>507.38862819611103</v>
+        <v>534.54478539989793</v>
       </c>
       <c r="G30" s="5">
-        <v>849.52154138876108</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+        <v>851.86508360702101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>1973.2203897654731</v>
+        <v>2008.4239577244234</v>
       </c>
       <c r="C31" s="5">
-        <v>2049.2286117722501</v>
+        <v>2088.6782203360731</v>
       </c>
       <c r="D31" s="5">
-        <v>1399.6065576790299</v>
+        <v>1439.7737882742294</v>
       </c>
       <c r="E31" s="5">
-        <v>729.02609697800733</v>
+        <v>702.77978171709822</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>884.38549946409216</v>
+        <v>889.37070436802992</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual/eu_wob_prices.xlsx
+++ b/data/manual/eu_wob_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBC795CF-7EF1-4F68-953A-923CE5A09F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E2E1759-80FE-4B62-9E4A-69193CF4B467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
@@ -600,7 +600,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -626,13 +626,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>1795</v>
+        <v>1784</v>
       </c>
       <c r="C3" s="3">
-        <v>2043</v>
+        <v>2050</v>
       </c>
       <c r="D3" s="3">
-        <v>1600.91</v>
+        <v>1634.34</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -643,16 +643,16 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1841.05</v>
+        <v>1899.73</v>
       </c>
       <c r="C4" s="3">
-        <v>2173.52</v>
+        <v>2257.02</v>
       </c>
       <c r="D4" s="3">
-        <v>1318.7</v>
+        <v>1339.6</v>
       </c>
       <c r="E4" s="3">
-        <v>525.77</v>
+        <v>542.91</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
@@ -664,16 +664,16 @@
         <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1534.9</v>
+        <v>1549.6</v>
       </c>
       <c r="C5" s="3">
-        <v>1767.5</v>
+        <v>1798.4</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>642.79999999999995</v>
+        <v>642.9</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -681,20 +681,20 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1623</v>
+        <v>1693</v>
       </c>
       <c r="C6" s="3">
-        <v>1835</v>
+        <v>1932</v>
       </c>
       <c r="D6" s="3">
-        <v>1360</v>
+        <v>1460</v>
       </c>
       <c r="E6" s="3">
         <v>869.6</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>714</v>
+        <v>734</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -702,13 +702,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1594.98</v>
+        <v>1594.46</v>
       </c>
       <c r="C7" s="3">
-        <v>1804.46</v>
+        <v>1832.56</v>
       </c>
       <c r="D7" s="3">
-        <v>1449.28</v>
+        <v>1468.19</v>
       </c>
       <c r="E7" s="3">
         <v>1059.51</v>
@@ -721,18 +721,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1713.5242345357628</v>
+        <v>1738.9211618257261</v>
       </c>
       <c r="C8" s="3">
-        <v>1843.9733895293582</v>
+        <v>1898.7551867219915</v>
       </c>
       <c r="D8" s="3">
-        <v>1347.9608280649559</v>
+        <v>1384.6473029045642</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>915.58200074377089</v>
+        <v>904.89626556016594</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -740,13 +740,13 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>2445.2232536986007</v>
+        <v>2458.6326364086308</v>
       </c>
       <c r="C9" s="3">
-        <v>2249.9264292784719</v>
+        <v>2276.7098733228995</v>
       </c>
       <c r="D9" s="3">
-        <v>2335.8035260440352</v>
+        <v>2362.5881188383696</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -776,13 +776,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>2140.3478260869565</v>
+        <v>2177</v>
       </c>
       <c r="C11" s="3">
-        <v>2317.652173913043</v>
+        <v>2346.0833333333298</v>
       </c>
       <c r="D11" s="3">
-        <v>1865.4152777777779</v>
+        <v>2015.0949999999996</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -793,18 +793,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>2038.33</v>
+        <v>2063.36</v>
       </c>
       <c r="C12" s="3">
-        <v>2199.34</v>
+        <v>2231.17</v>
       </c>
       <c r="D12" s="3">
-        <v>1696.18</v>
+        <v>1724.27</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>1019.64</v>
+        <v>1022.69</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -812,18 +812,18 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="C13" s="3">
-        <v>2266</v>
+        <v>2286</v>
       </c>
       <c r="D13" s="3">
-        <v>1343</v>
+        <v>1333.1</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>1089</v>
+        <v>1090.25</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -831,10 +831,10 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>2002</v>
+        <v>2028</v>
       </c>
       <c r="C14" s="3">
-        <v>1996</v>
+        <v>2040</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3">
@@ -848,20 +848,20 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>1615.0576393983818</v>
+        <v>1634.3377808900764</v>
       </c>
       <c r="C15" s="3">
-        <v>1859.8302373451172</v>
+        <v>1878.9402792422732</v>
       </c>
       <c r="D15" s="3">
-        <v>1859.8302373451172</v>
+        <v>1878.9402792422732</v>
       </c>
       <c r="E15" s="3">
-        <v>1097.2287458900892</v>
+        <v>1095.3523651910079</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>987.25766439386553</v>
+        <v>981.08610384266979</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -869,13 +869,13 @@
         <v>24</v>
       </c>
       <c r="B16" s="3">
-        <v>1838.7</v>
+        <v>1836.4</v>
       </c>
       <c r="C16" s="3">
-        <v>1900.8</v>
+        <v>1905.6</v>
       </c>
       <c r="D16" s="3">
-        <v>1348.75</v>
+        <v>1353.65</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -886,20 +886,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>1987.99</v>
+        <v>2003.03</v>
       </c>
       <c r="C17" s="3">
-        <v>2078.92</v>
+        <v>2115.09</v>
       </c>
       <c r="D17" s="3">
-        <v>1857.45</v>
+        <v>1887.55</v>
       </c>
       <c r="E17" s="3">
-        <v>646.17999999999995</v>
+        <v>662.55</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>771.37</v>
+        <v>770.2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -907,18 +907,18 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1816.8</v>
+        <v>1844.2</v>
       </c>
       <c r="C18" s="3">
-        <v>1913.5</v>
+        <v>1972</v>
       </c>
       <c r="D18" s="3">
-        <v>1597.68</v>
+        <v>1656.19</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -926,18 +926,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1770.05</v>
+        <v>1777.86</v>
       </c>
       <c r="C19" s="3">
-        <v>2031.03</v>
+        <v>2051.9</v>
       </c>
       <c r="D19" s="3">
-        <v>1381.47</v>
+        <v>1397.81</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>752.45</v>
+        <v>748.4</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -948,15 +948,15 @@
         <v>1727</v>
       </c>
       <c r="C20" s="3">
-        <v>1922</v>
+        <v>1963</v>
       </c>
       <c r="D20" s="3">
-        <v>1415</v>
+        <v>1454</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>687</v>
+        <v>717</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -981,16 +981,16 @@
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>2328.81</v>
+        <v>2352.6</v>
       </c>
       <c r="C22" s="3">
-        <v>2383.12</v>
+        <v>2415.46</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>938.5</v>
+        <v>933.94</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -998,22 +998,22 @@
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1480.8336577669313</v>
+        <v>1507.7066273662226</v>
       </c>
       <c r="C23" s="3">
-        <v>1685.5407719552709</v>
+        <v>1728.178662026907</v>
       </c>
       <c r="D23" s="3">
-        <v>1463.6894449163976</v>
+        <v>1509.040927607545</v>
       </c>
       <c r="E23" s="3">
-        <v>717.28883590534349</v>
+        <v>727.4702373614009</v>
       </c>
       <c r="F23" s="3">
-        <v>555.43504138104333</v>
+        <v>598.83810686382083</v>
       </c>
       <c r="G23" s="3">
-        <v>692.2868079227153</v>
+        <v>682.85833340019246</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1021,20 +1021,20 @@
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>1954</v>
+        <v>1986</v>
       </c>
       <c r="C24" s="3">
-        <v>2026</v>
+        <v>2066</v>
       </c>
       <c r="D24" s="3">
-        <v>2024</v>
+        <v>2078</v>
       </c>
       <c r="E24" s="3">
-        <v>1032.83</v>
+        <v>1047.23</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1042,20 +1042,20 @@
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>1816.3889684130165</v>
+        <v>1816.07877495048</v>
       </c>
       <c r="C25" s="3">
-        <v>2029.6688615325893</v>
+        <v>1939.7703032149932</v>
       </c>
       <c r="D25" s="3">
-        <v>1394.7094188376755</v>
+        <v>1441.4673167758647</v>
       </c>
       <c r="E25" s="3">
-        <v>843.17014982345654</v>
+        <v>854.0530245314643</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>885.02147151445752</v>
+        <v>886.12867591040686</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1063,16 +1063,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>1696</v>
+        <v>1724</v>
       </c>
       <c r="C26" s="3">
-        <v>1832</v>
+        <v>1862</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>774</v>
+        <v>803</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1080,18 +1080,18 @@
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1577.66</v>
+        <v>1562.06</v>
       </c>
       <c r="C27" s="3">
-        <v>1844.53</v>
+        <v>1812.73</v>
       </c>
       <c r="D27" s="3">
-        <v>1433.31</v>
+        <v>1462.67</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>971.54</v>
+        <v>992.32</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1099,20 +1099,20 @@
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1705.449251</v>
+        <v>1723.7045639999999</v>
       </c>
       <c r="C28" s="3">
-        <v>1828.8145149999998</v>
+        <v>1861.0012769999998</v>
       </c>
       <c r="D28" s="3">
-        <v>1323.2560000000001</v>
+        <v>1347.866</v>
       </c>
       <c r="E28" s="3">
-        <v>648.80999999999995</v>
+        <v>657.02099999999996</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>1075.7977460000002</v>
+        <v>1083.163311</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1120,16 +1120,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1408.2356149440959</v>
+        <v>1435.2240422363611</v>
       </c>
       <c r="C29" s="3">
-        <v>1779.8381965275885</v>
+        <v>1817.4270114164522</v>
       </c>
       <c r="D29" s="3">
-        <v>1670.3026997545678</v>
+        <v>1703.0819908848878</v>
       </c>
       <c r="E29" s="3">
-        <v>984.9104626852104</v>
+        <v>1008.4382473715085</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1139,22 +1139,22 @@
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>1923.6200449931841</v>
+        <v>1941.8563648897593</v>
       </c>
       <c r="C30" s="5">
-        <v>2033.1381469525866</v>
+        <v>2063.3660614777104</v>
       </c>
       <c r="D30" s="5">
-        <v>1458.7022912064526</v>
+        <v>1475.4712472734063</v>
       </c>
       <c r="E30" s="5">
-        <v>681.83587524575557</v>
+        <v>690.42170889912961</v>
       </c>
       <c r="F30" s="5">
-        <v>534.54478539989793</v>
+        <v>576.31543470301335</v>
       </c>
       <c r="G30" s="5">
-        <v>851.86508360702101</v>
+        <v>850.55270109555829</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
@@ -1162,20 +1162,20 @@
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>2008.4239577244234</v>
+        <v>2025.3816620988741</v>
       </c>
       <c r="C31" s="5">
-        <v>2088.6782203360731</v>
+        <v>2119.6273842452551</v>
       </c>
       <c r="D31" s="5">
-        <v>1439.7737882742294</v>
+        <v>1455.3016136959684</v>
       </c>
       <c r="E31" s="5">
-        <v>702.77978171709822</v>
+        <v>711.53086487468147</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>889.37070436802992</v>
+        <v>890.11739509412644</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual/eu_wob_prices.xlsx
+++ b/data/manual/eu_wob_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E2E1759-80FE-4B62-9E4A-69193CF4B467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5078D2A3-31C5-4F0A-BDD7-AB06A0DADDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
@@ -600,7 +600,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -629,10 +629,10 @@
         <v>1784</v>
       </c>
       <c r="C3" s="3">
-        <v>2050</v>
+        <v>1993</v>
       </c>
       <c r="D3" s="3">
-        <v>1634.34</v>
+        <v>1607.09</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -643,20 +643,20 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1899.73</v>
+        <v>1884.79</v>
       </c>
       <c r="C4" s="3">
-        <v>2257.02</v>
+        <v>2207.7600000000002</v>
       </c>
       <c r="D4" s="3">
-        <v>1339.6</v>
+        <v>1253.5</v>
       </c>
       <c r="E4" s="3">
-        <v>542.91</v>
+        <v>522.25</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>792</v>
+        <v>818</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -664,16 +664,16 @@
         <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1549.6</v>
+        <v>1571.2</v>
       </c>
       <c r="C5" s="3">
-        <v>1798.4</v>
+        <v>1812.9</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>642.9</v>
+        <v>642.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -681,20 +681,20 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1693</v>
+        <v>1723</v>
       </c>
       <c r="C6" s="3">
-        <v>1932</v>
+        <v>1989</v>
       </c>
       <c r="D6" s="3">
-        <v>1460</v>
+        <v>1500</v>
       </c>
       <c r="E6" s="3">
         <v>869.6</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>734</v>
+        <v>744</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -702,13 +702,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1594.46</v>
+        <v>1601.84</v>
       </c>
       <c r="C7" s="3">
-        <v>1832.56</v>
+        <v>1856.86</v>
       </c>
       <c r="D7" s="3">
-        <v>1468.19</v>
+        <v>1470.71</v>
       </c>
       <c r="E7" s="3">
         <v>1059.51</v>
@@ -721,18 +721,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1738.9211618257261</v>
+        <v>1742.1026448884836</v>
       </c>
       <c r="C8" s="3">
-        <v>1898.7551867219915</v>
+        <v>1903.449133571014</v>
       </c>
       <c r="D8" s="3">
-        <v>1384.6473029045642</v>
+        <v>1347.5665367714121</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>904.89626556016594</v>
+        <v>906.76560815852747</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -740,13 +740,13 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>2458.6326364086308</v>
+        <v>2524.3809447365252</v>
       </c>
       <c r="C9" s="3">
-        <v>2276.7098733228995</v>
+        <v>2274.2170673302026</v>
       </c>
       <c r="D9" s="3">
-        <v>2362.5881188383696</v>
+        <v>2262.0433171462587</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -757,13 +757,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>1772</v>
+        <v>1812</v>
       </c>
       <c r="C10" s="3">
-        <v>1880</v>
+        <v>1922</v>
       </c>
       <c r="D10" s="3">
-        <v>1421</v>
+        <v>1442</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -776,13 +776,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>2177</v>
+        <v>2203.2631578947376</v>
       </c>
       <c r="C11" s="3">
-        <v>2346.0833333333298</v>
+        <v>2333.5789473684217</v>
       </c>
       <c r="D11" s="3">
-        <v>2015.0949999999996</v>
+        <v>1828.4979166666669</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -793,18 +793,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>2063.36</v>
+        <v>2073.16</v>
       </c>
       <c r="C12" s="3">
-        <v>2231.17</v>
+        <v>2208.5500000000002</v>
       </c>
       <c r="D12" s="3">
-        <v>1724.27</v>
+        <v>1672.35</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>1022.69</v>
+        <v>1016.49</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -812,18 +812,18 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>2245</v>
+        <v>2236</v>
       </c>
       <c r="C13" s="3">
-        <v>2286</v>
+        <v>2232</v>
       </c>
       <c r="D13" s="3">
-        <v>1333.1</v>
+        <v>1401.8</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>1090.25</v>
+        <v>1082.75</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -831,10 +831,10 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>2028</v>
+        <v>2046</v>
       </c>
       <c r="C14" s="3">
-        <v>2040</v>
+        <v>2023</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3">
@@ -848,20 +848,20 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>1634.3377808900764</v>
+        <v>1638.4443562812744</v>
       </c>
       <c r="C15" s="3">
-        <v>1878.9402792422732</v>
+        <v>1858.5273208593962</v>
       </c>
       <c r="D15" s="3">
-        <v>1878.9402792422732</v>
+        <v>1858.5273208593962</v>
       </c>
       <c r="E15" s="3">
-        <v>1095.3523651910079</v>
+        <v>1089.9409908055441</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>981.08610384266979</v>
+        <v>974.57001359250785</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -869,13 +869,13 @@
         <v>24</v>
       </c>
       <c r="B16" s="3">
-        <v>1836.4</v>
+        <v>1836.7</v>
       </c>
       <c r="C16" s="3">
-        <v>1905.6</v>
+        <v>1930.6</v>
       </c>
       <c r="D16" s="3">
-        <v>1353.65</v>
+        <v>1328.1</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -886,20 +886,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>2003.03</v>
+        <v>2016.7</v>
       </c>
       <c r="C17" s="3">
-        <v>2115.09</v>
+        <v>2123.46</v>
       </c>
       <c r="D17" s="3">
-        <v>1887.55</v>
+        <v>1863</v>
       </c>
       <c r="E17" s="3">
-        <v>662.55</v>
+        <v>656.55</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>770.2</v>
+        <v>767.54</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -907,18 +907,18 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1844.2</v>
+        <v>1841.2</v>
       </c>
       <c r="C18" s="3">
-        <v>1972</v>
+        <v>1951.67</v>
       </c>
       <c r="D18" s="3">
-        <v>1656.19</v>
+        <v>1635.86</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>910</v>
+        <v>913.75</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -926,18 +926,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1777.86</v>
+        <v>1790.01</v>
       </c>
       <c r="C19" s="3">
-        <v>2051.9</v>
+        <v>2043.29</v>
       </c>
       <c r="D19" s="3">
-        <v>1397.81</v>
+        <v>1359.15</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>748.4</v>
+        <v>749.69</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -945,18 +945,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1727</v>
+        <v>1748</v>
       </c>
       <c r="C20" s="3">
-        <v>1963</v>
+        <v>1865</v>
       </c>
       <c r="D20" s="3">
-        <v>1454</v>
+        <v>1355</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>717</v>
+        <v>704</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -981,16 +981,16 @@
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>2352.6</v>
+        <v>2349.94</v>
       </c>
       <c r="C22" s="3">
-        <v>2415.46</v>
+        <v>2325.88</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>933.94</v>
+        <v>932.77</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -998,22 +998,22 @@
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1507.7066273662226</v>
+        <v>1524.6598078411496</v>
       </c>
       <c r="C23" s="3">
-        <v>1728.178662026907</v>
+        <v>1669.3621234675738</v>
       </c>
       <c r="D23" s="3">
-        <v>1509.040927607545</v>
+        <v>1450.208521795563</v>
       </c>
       <c r="E23" s="3">
-        <v>727.4702373614009</v>
+        <v>726.2870047572444</v>
       </c>
       <c r="F23" s="3">
-        <v>598.83810686382083</v>
+        <v>551.71092376358149</v>
       </c>
       <c r="G23" s="3">
-        <v>682.85833340019246</v>
+        <v>672.15237902648209</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1021,20 +1021,20 @@
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>1986</v>
+        <v>2013</v>
       </c>
       <c r="C24" s="3">
-        <v>2066</v>
+        <v>2029</v>
       </c>
       <c r="D24" s="3">
-        <v>2078</v>
+        <v>2038</v>
       </c>
       <c r="E24" s="3">
-        <v>1047.23</v>
+        <v>1064.19</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1042,20 +1042,20 @@
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>1816.07877495048</v>
+        <v>1812.6604166161708</v>
       </c>
       <c r="C25" s="3">
-        <v>1939.7703032149932</v>
+        <v>1937.9022784539115</v>
       </c>
       <c r="D25" s="3">
-        <v>1441.4673167758647</v>
+        <v>1414.564809688927</v>
       </c>
       <c r="E25" s="3">
-        <v>854.0530245314643</v>
+        <v>851.39766556739016</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>886.12867591040686</v>
+        <v>884.86894597098205</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1063,16 +1063,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>1724</v>
+        <v>1753</v>
       </c>
       <c r="C26" s="3">
-        <v>1862</v>
+        <v>1883</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1080,18 +1080,18 @@
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1562.06</v>
+        <v>1614.65</v>
       </c>
       <c r="C27" s="3">
-        <v>1812.73</v>
+        <v>1900.15</v>
       </c>
       <c r="D27" s="3">
-        <v>1462.67</v>
+        <v>1536.03</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>992.32</v>
+        <v>996.74</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1099,20 +1099,20 @@
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1723.7045639999999</v>
+        <v>1732.493827</v>
       </c>
       <c r="C28" s="3">
-        <v>1861.0012769999998</v>
+        <v>1865.4099509999999</v>
       </c>
       <c r="D28" s="3">
-        <v>1347.866</v>
+        <v>1322.7009999999998</v>
       </c>
       <c r="E28" s="3">
-        <v>657.02099999999996</v>
+        <v>672.1</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>1083.163311</v>
+        <v>1087.589377</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1120,16 +1120,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1435.2240422363611</v>
+        <v>1471.0171017101709</v>
       </c>
       <c r="C29" s="3">
-        <v>1817.4270114164522</v>
+        <v>1730.3330333033302</v>
       </c>
       <c r="D29" s="3">
-        <v>1703.0819908848878</v>
+        <v>1640.7740774077408</v>
       </c>
       <c r="E29" s="3">
-        <v>1008.4382473715085</v>
+        <v>1005.2205220522052</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1139,22 +1139,22 @@
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>1941.8563648897593</v>
+        <v>1949.9923900848278</v>
       </c>
       <c r="C30" s="5">
-        <v>2063.3660614777104</v>
+        <v>2039.1469620832606</v>
       </c>
       <c r="D30" s="5">
-        <v>1475.4712472734063</v>
+        <v>1472.9454249041821</v>
       </c>
       <c r="E30" s="5">
-        <v>690.42170889912961</v>
+        <v>701.93145851243844</v>
       </c>
       <c r="F30" s="5">
-        <v>576.31543470301335</v>
+        <v>530.9607341530043</v>
       </c>
       <c r="G30" s="5">
-        <v>850.55270109555829</v>
+        <v>845.69975867366531</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
@@ -1162,20 +1162,20 @@
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>2025.3816620988741</v>
+        <v>2030.2435921562176</v>
       </c>
       <c r="C31" s="5">
-        <v>2119.6273842452551</v>
+        <v>2099.4518634840733</v>
       </c>
       <c r="D31" s="5">
-        <v>1455.3016136959684</v>
+        <v>1455.9231829986054</v>
       </c>
       <c r="E31" s="5">
-        <v>711.53086487468147</v>
+        <v>723.70330432012884</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>890.11739509412644</v>
+        <v>886.5567999632932</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual/eu_wob_prices.xlsx
+++ b/data/manual/eu_wob_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5078D2A3-31C5-4F0A-BDD7-AB06A0DADDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{543A262B-DDEA-4D15-802F-4CDD9E98D923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
@@ -600,7 +600,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -626,13 +626,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>1784</v>
+        <v>1912</v>
       </c>
       <c r="C3" s="3">
-        <v>1993</v>
+        <v>2126</v>
       </c>
       <c r="D3" s="3">
-        <v>1607.09</v>
+        <v>1710.52</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -643,20 +643,20 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1884.79</v>
+        <v>1937.96</v>
       </c>
       <c r="C4" s="3">
-        <v>2207.7600000000002</v>
+        <v>2254.2399999999998</v>
       </c>
       <c r="D4" s="3">
-        <v>1253.5</v>
+        <v>1438.9</v>
       </c>
       <c r="E4" s="3">
-        <v>522.25</v>
+        <v>553.77</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>818</v>
+        <v>870</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -681,20 +681,20 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1723</v>
+        <v>1731</v>
       </c>
       <c r="C6" s="3">
-        <v>1989</v>
+        <v>1908</v>
       </c>
       <c r="D6" s="3">
-        <v>1500</v>
+        <v>1580</v>
       </c>
       <c r="E6" s="3">
         <v>869.6</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>744</v>
+        <v>734</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -702,13 +702,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1601.84</v>
+        <v>1632.28</v>
       </c>
       <c r="C7" s="3">
-        <v>1856.86</v>
+        <v>1894.53</v>
       </c>
       <c r="D7" s="3">
-        <v>1470.71</v>
+        <v>1520.38</v>
       </c>
       <c r="E7" s="3">
         <v>1059.51</v>
@@ -721,18 +721,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1742.1026448884836</v>
+        <v>1806.3396288796134</v>
       </c>
       <c r="C8" s="3">
-        <v>1903.449133571014</v>
+        <v>1958.4659255279582</v>
       </c>
       <c r="D8" s="3">
-        <v>1347.5665367714121</v>
+        <v>1477.9518122081251</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>906.76560815852747</v>
+        <v>897.30131834524946</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -740,13 +740,13 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>2524.3809447365252</v>
+        <v>2631.5789473684213</v>
       </c>
       <c r="C9" s="3">
-        <v>2274.2170673302026</v>
+        <v>2434.9129050383967</v>
       </c>
       <c r="D9" s="3">
-        <v>2262.0433171462587</v>
+        <v>2395.9810558424533</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -776,13 +776,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>2203.2631578947376</v>
+        <v>2323.150000000001</v>
       </c>
       <c r="C11" s="3">
-        <v>2333.5789473684217</v>
+        <v>2477.8500000000004</v>
       </c>
       <c r="D11" s="3">
-        <v>1828.4979166666669</v>
+        <v>1989.86958333333</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -793,18 +793,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>2073.16</v>
+        <v>2114.94</v>
       </c>
       <c r="C12" s="3">
-        <v>2208.5500000000002</v>
+        <v>2257.13</v>
       </c>
       <c r="D12" s="3">
-        <v>1672.35</v>
+        <v>1792.48</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>1016.49</v>
+        <v>1015.4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -812,18 +812,18 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>2236</v>
+        <v>2331</v>
       </c>
       <c r="C13" s="3">
-        <v>2232</v>
+        <v>2328</v>
       </c>
       <c r="D13" s="3">
-        <v>1401.8</v>
+        <v>1520.9</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>1082.75</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -831,10 +831,10 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>2046</v>
+        <v>2093</v>
       </c>
       <c r="C14" s="3">
-        <v>2023</v>
+        <v>2054</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3">
@@ -848,20 +848,20 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>1638.4443562812744</v>
+        <v>1643.6321619247865</v>
       </c>
       <c r="C15" s="3">
-        <v>1858.5273208593962</v>
+        <v>1864.4119750966993</v>
       </c>
       <c r="D15" s="3">
-        <v>1858.5273208593962</v>
+        <v>1864.4119750966993</v>
       </c>
       <c r="E15" s="3">
-        <v>1089.9409908055441</v>
+        <v>1093.3920704845816</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>974.57001359250785</v>
+        <v>977.65579419721996</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -869,13 +869,13 @@
         <v>24</v>
       </c>
       <c r="B16" s="3">
-        <v>1836.7</v>
+        <v>1854.6</v>
       </c>
       <c r="C16" s="3">
-        <v>1930.6</v>
+        <v>1953.8</v>
       </c>
       <c r="D16" s="3">
-        <v>1328.1</v>
+        <v>1410.55</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -886,20 +886,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>2016.7</v>
+        <v>2034.68</v>
       </c>
       <c r="C17" s="3">
-        <v>2123.46</v>
+        <v>2141.8200000000002</v>
       </c>
       <c r="D17" s="3">
-        <v>1863</v>
+        <v>1964.95</v>
       </c>
       <c r="E17" s="3">
-        <v>656.55</v>
+        <v>670.36</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>767.54</v>
+        <v>769.04</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -907,18 +907,18 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1841.2</v>
+        <v>1939.2</v>
       </c>
       <c r="C18" s="3">
-        <v>1951.67</v>
+        <v>2047.67</v>
       </c>
       <c r="D18" s="3">
-        <v>1635.86</v>
+        <v>1731.86</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>913.75</v>
+        <v>911.67</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -926,18 +926,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1790.01</v>
+        <v>1883.98</v>
       </c>
       <c r="C19" s="3">
-        <v>2043.29</v>
+        <v>2128.2399999999998</v>
       </c>
       <c r="D19" s="3">
-        <v>1359.15</v>
+        <v>1472.26</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>749.69</v>
+        <v>770.33</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -945,18 +945,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1748</v>
+        <v>1868</v>
       </c>
       <c r="C20" s="3">
-        <v>1865</v>
+        <v>2024</v>
       </c>
       <c r="D20" s="3">
-        <v>1355</v>
+        <v>1510</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>704</v>
+        <v>738</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -981,16 +981,16 @@
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>2349.94</v>
+        <v>2465.83</v>
       </c>
       <c r="C22" s="3">
-        <v>2325.88</v>
+        <v>2442.2399999999998</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>932.77</v>
+        <v>931.1</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -998,22 +998,22 @@
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1524.6598078411496</v>
+        <v>1811.6151270136215</v>
       </c>
       <c r="C23" s="3">
-        <v>1669.3621234675738</v>
+        <v>1982.0406158447261</v>
       </c>
       <c r="D23" s="3">
-        <v>1450.208521795563</v>
+        <v>1577.9070023665197</v>
       </c>
       <c r="E23" s="3">
-        <v>726.2870047572444</v>
+        <v>744.57448607040601</v>
       </c>
       <c r="F23" s="3">
-        <v>551.71092376358149</v>
+        <v>592.83218171485248</v>
       </c>
       <c r="G23" s="3">
-        <v>672.15237902648209</v>
+        <v>686.86402384551252</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1021,20 +1021,20 @@
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>2013</v>
+        <v>2093</v>
       </c>
       <c r="C24" s="3">
-        <v>2029</v>
+        <v>2104</v>
       </c>
       <c r="D24" s="3">
-        <v>2038</v>
+        <v>2114</v>
       </c>
       <c r="E24" s="3">
-        <v>1064.19</v>
+        <v>1048</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>886</v>
+        <v>890</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1042,20 +1042,20 @@
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>1812.6604166161708</v>
+        <v>1851.3147622765096</v>
       </c>
       <c r="C25" s="3">
-        <v>1937.9022784539115</v>
+        <v>1941.5087872960264</v>
       </c>
       <c r="D25" s="3">
-        <v>1414.564809688927</v>
+        <v>1416.4321483653537</v>
       </c>
       <c r="E25" s="3">
-        <v>851.39766556739016</v>
+        <v>844.53245492107612</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>884.86894597098205</v>
+        <v>890.41299339286729</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1063,16 +1063,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>1753</v>
+        <v>1774</v>
       </c>
       <c r="C26" s="3">
-        <v>1883</v>
+        <v>1908</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1080,18 +1080,18 @@
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1614.65</v>
+        <v>1633.44</v>
       </c>
       <c r="C27" s="3">
-        <v>1900.15</v>
+        <v>1879.92</v>
       </c>
       <c r="D27" s="3">
-        <v>1536.03</v>
+        <v>1491.4</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>996.74</v>
+        <v>994.83</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1099,20 +1099,20 @@
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1732.493827</v>
+        <v>1815.9729689999999</v>
       </c>
       <c r="C28" s="3">
-        <v>1865.4099509999999</v>
+        <v>1795.450398</v>
       </c>
       <c r="D28" s="3">
-        <v>1322.7009999999998</v>
+        <v>1396.2440000000001</v>
       </c>
       <c r="E28" s="3">
-        <v>672.1</v>
+        <v>624.39700000000005</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>1087.589377</v>
+        <v>1088.8231500000002</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1120,16 +1120,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1471.0171017101709</v>
+        <v>1587.6187063250313</v>
       </c>
       <c r="C29" s="3">
-        <v>1730.3330333033302</v>
+        <v>1904.0494535029563</v>
       </c>
       <c r="D29" s="3">
-        <v>1640.7740774077408</v>
+        <v>1765.0062712775489</v>
       </c>
       <c r="E29" s="3">
-        <v>1005.2205220522052</v>
+        <v>1008.4214298512811</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1139,22 +1139,22 @@
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>1949.9923900848278</v>
+        <v>2041.6684660061321</v>
       </c>
       <c r="C30" s="5">
-        <v>2039.1469620832606</v>
+        <v>2107.3855574757486</v>
       </c>
       <c r="D30" s="5">
-        <v>1472.9454249041821</v>
+        <v>1595.2382987100923</v>
       </c>
       <c r="E30" s="5">
-        <v>701.93145851243844</v>
+        <v>668.18125247344585</v>
       </c>
       <c r="F30" s="5">
-        <v>530.9607341530043</v>
+        <v>570.53539611938243</v>
       </c>
       <c r="G30" s="5">
-        <v>845.69975867366531</v>
+        <v>850.28188678964614</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
@@ -1162,20 +1162,20 @@
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>2030.2435921562176</v>
+        <v>2099.8495948841119</v>
       </c>
       <c r="C31" s="5">
-        <v>2099.4518634840733</v>
+        <v>2137.6925501645705</v>
       </c>
       <c r="D31" s="5">
-        <v>1455.9231829986054</v>
+        <v>1578.7497009047352</v>
       </c>
       <c r="E31" s="5">
-        <v>723.70330432012884</v>
+        <v>688.06590904759287</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>886.5567999632932</v>
+        <v>888.79971866615824</v>
       </c>
     </row>
   </sheetData>
